--- a/research/META/Reports/META_DCF_Model.xlsx
+++ b/research/META/Reports/META_DCF_Model.xlsx
@@ -2114,9 +2114,10 @@
       <c r="D54" s="46" t="n">
         <v>61680</v>
       </c>
-      <c r="E54" s="45">
-        <f> Y5 Revenue × Terminal FCF Margin × (1 + Terminal Growth)</f>
-        <v/>
+      <c r="E54" s="45" t="inlineStr">
+        <is>
+          <t>= Y5 Revenue × Terminal FCF Margin × (1 + Terminal Growth)</t>
+        </is>
       </c>
     </row>
     <row r="55" ht="17" customHeight="1">
@@ -2134,9 +2135,10 @@
       <c r="D55" s="46" t="n">
         <v>622071</v>
       </c>
-      <c r="E55" s="45">
-        <f> Terminal FCF / (WACC − Terminal Growth Rate)</f>
-        <v/>
+      <c r="E55" s="45" t="inlineStr">
+        <is>
+          <t>= Terminal FCF / (WACC − Terminal Growth Rate)</t>
+        </is>
       </c>
     </row>
     <row r="56" ht="17" customHeight="1">
@@ -2154,9 +2156,10 @@
       <c r="D56" s="46" t="n">
         <v>369360</v>
       </c>
-      <c r="E56" s="45">
-        <f> Terminal Value × Y5 Discount Factor</f>
-        <v/>
+      <c r="E56" s="45" t="inlineStr">
+        <is>
+          <t>= Terminal Value × Y5 Discount Factor</t>
+        </is>
       </c>
     </row>
     <row r="57" ht="17" customHeight="1">
@@ -2174,9 +2177,10 @@
       <c r="D57" s="44" t="n">
         <v>433087</v>
       </c>
-      <c r="E57" s="45">
-        <f> Sum PV FCF + PV Terminal Value</f>
-        <v/>
+      <c r="E57" s="45" t="inlineStr">
+        <is>
+          <t>= Sum PV FCF + PV Terminal Value</t>
+        </is>
       </c>
     </row>
     <row r="58" ht="17" customHeight="1">
@@ -2211,9 +2215,10 @@
       <c r="D59" s="44" t="n">
         <v>455935</v>
       </c>
-      <c r="E59" s="45">
-        <f> Enterprise Value + Net Cash</f>
-        <v/>
+      <c r="E59" s="45" t="inlineStr">
+        <is>
+          <t>= Enterprise Value + Net Cash</t>
+        </is>
       </c>
     </row>
     <row r="60" ht="17" customHeight="1">
@@ -2248,9 +2253,10 @@
       <c r="D61" s="51" t="n">
         <v>177.82</v>
       </c>
-      <c r="E61" s="45">
-        <f> Equity Value ÷ Shares Outstanding</f>
-        <v/>
+      <c r="E61" s="45" t="inlineStr">
+        <is>
+          <t>= Equity Value ÷ Shares Outstanding</t>
+        </is>
       </c>
     </row>
     <row r="62" ht="17" customHeight="1">
@@ -2360,9 +2366,10 @@
       <c r="B69" s="65" t="n">
         <v>546.04</v>
       </c>
-      <c r="C69" s="66">
-        <f> Sum of (weight × IV)</f>
-        <v/>
+      <c r="C69" s="66" t="inlineStr">
+        <is>
+          <t>= Sum of (weight × IV)</t>
+        </is>
       </c>
     </row>
     <row r="70" ht="17" customHeight="1">
